--- a/product_upload/packages/19/file.xlsx
+++ b/product_upload/packages/19/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>BENZAC AC 5% GEL</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-7DB79766270E</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1034,6 +1044,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>BENZAC AC 2.5% GEL</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-FD9531901715</t>
         </is>
       </c>
@@ -1057,7 +1072,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>BETADERM 0.1% ointment</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-7CF2A1925861</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1410,6 +1430,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>BETAGEN</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-C6F0FE61E003</t>
         </is>
       </c>
@@ -1433,7 +1458,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1608,6 +1633,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>BETATEN 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-061079E90E4C</t>
         </is>
       </c>
@@ -1631,7 +1661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1794,6 +1824,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>BETATEN 25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-2E57148CAC9A</t>
         </is>
       </c>
@@ -1817,7 +1852,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1984,6 +2019,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>BETATEN 100MG F.C. TABS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-07970C411451</t>
         </is>
       </c>
@@ -2007,7 +2047,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2180,6 +2220,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>BETASERC 8 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-9EC2146C2B9C</t>
         </is>
       </c>
@@ -2203,7 +2248,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2376,6 +2421,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>BETASERC 24 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-8CA9634A3FE2</t>
         </is>
       </c>
@@ -2399,7 +2449,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2566,6 +2616,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>BETASAL OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-41BF4831E338</t>
         </is>
       </c>
@@ -2589,7 +2644,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2756,6 +2811,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>BETAMED-N OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-6EF240C3F12F</t>
         </is>
       </c>
@@ -2779,7 +2839,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2946,6 +3006,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>BETAMED-N CREAM</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-3C9F23C2E7CE</t>
         </is>
       </c>
@@ -2969,7 +3034,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3136,6 +3201,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>BETAMED 0.1% TOPICAL OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-E16CB7D9763A</t>
         </is>
       </c>
@@ -3159,7 +3229,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3326,6 +3396,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>BETAMED 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-BA6AF9FA559A</t>
         </is>
       </c>
@@ -3349,7 +3424,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3520,6 +3595,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>BETAGEN</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-0F048059F9C6</t>
         </is>
       </c>
@@ -3543,7 +3623,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3712,6 +3792,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>BETASERC 16MG TAB</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-84120B42786C</t>
         </is>
       </c>
@@ -3735,7 +3820,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3910,6 +3995,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>BANEOCIN POWDER</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-E21A829627D2</t>
         </is>
       </c>
@@ -3933,7 +4023,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4104,6 +4194,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>BALKATRIN TAB</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-9A5F51FDD012</t>
         </is>
       </c>
@@ -4127,7 +4222,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4294,6 +4389,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>BALKATRIN SUSP</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-40B46E30AB66</t>
         </is>
       </c>
@@ -4317,7 +4417,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4484,6 +4584,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>BANEOCIN POWDER</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-F7C8FE45D904</t>
         </is>
       </c>
@@ -4507,7 +4612,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4666,6 +4771,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>BALANCED SALT SOLUTION AMPOULE</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-E7E7DBA8E8F6</t>
         </is>
       </c>
@@ -4689,7 +4799,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4846,6 +4956,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CATALIN OPH. SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-AC0D50D1A376</t>
         </is>
       </c>
@@ -4869,7 +4984,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5040,6 +5155,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>BENDAZOLE 100 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-98E45866F12A</t>
         </is>
       </c>
@@ -5063,7 +5183,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5218,6 +5338,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>BEKUNIS TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-56C456BEEE5B</t>
         </is>
       </c>
@@ -5241,7 +5366,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5408,6 +5533,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>BEFOLVIT 5 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-D93757D1E795</t>
         </is>
       </c>
@@ -5431,7 +5561,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5606,6 +5736,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>BEFOLVIT 1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-A6497FBA97C5</t>
         </is>
       </c>
@@ -5629,7 +5764,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5792,6 +5927,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>BE BE VIT ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-7FA5A5061EB8</t>
         </is>
       </c>
@@ -5815,7 +5955,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5986,6 +6126,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>BCG VACCINE AJ Vaccines 0.75MG-VIAL</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-35CDF6698370</t>
         </is>
       </c>
@@ -6009,7 +6154,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6172,6 +6317,11 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>BAUMALGINE OINT</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-2E280C912D64</t>
         </is>
       </c>
@@ -6195,7 +6345,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6360,6 +6510,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>BATRAMYCIN POWDER</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-DC35ACA0F359</t>
         </is>
       </c>
@@ -6383,7 +6538,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6550,6 +6705,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-FFDD02D7E4C2</t>
         </is>
       </c>
@@ -6573,7 +6733,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6736,6 +6896,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-9CF43F3D119F</t>
         </is>
       </c>
@@ -6759,7 +6924,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6930,6 +7095,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>GONAL-F 900 IU solution for injection in pre-filled pen</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-3E9F6843C392</t>
         </is>
       </c>
@@ -6953,7 +7123,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7124,6 +7294,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>GONAL-F 450 IU solution for injection in pre-filled pen</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-1F9555300F8F</t>
         </is>
       </c>
@@ -7147,7 +7322,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7322,6 +7497,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>GONAL-F 300 IU solution for injection in pre-filled pen</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-D22D43689548</t>
         </is>
       </c>
@@ -7345,7 +7525,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7504,6 +7684,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>GUAPHAN</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-6EBA9DA300B9</t>
         </is>
       </c>
@@ -7527,7 +7712,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7698,6 +7883,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>GUAPHAN DM</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-0E9F3B7518B1</t>
         </is>
       </c>
@@ -7721,7 +7911,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7880,6 +8070,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>GYNO-DAKTARIN OVULES 400 MG.</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-C2E24894279F</t>
         </is>
       </c>
@@ -7903,7 +8098,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8066,6 +8261,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>GYNO-DAKTARIN CREAM WITH 16 APPLICATORS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-1872EEE7A993</t>
         </is>
       </c>
@@ -8089,7 +8289,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8264,6 +8464,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>GYNO-CORYL 150 MG VAGINAL OVULES</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-FC59389BEB6F</t>
         </is>
       </c>
@@ -8287,7 +8492,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8456,6 +8661,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>GYNO-CANDIZOL 400 MG VAGINAL OVULES</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-C111E6392E4A</t>
         </is>
       </c>
@@ -8479,7 +8689,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8652,6 +8862,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>GYNO-CANDIZOL 200 MG VAGINAL OVULES</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-039C631781B3</t>
         </is>
       </c>
@@ -8675,7 +8890,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8850,6 +9065,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>GYNERA 21 TAB</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-2D737325052A</t>
         </is>
       </c>
@@ -8873,7 +9093,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9032,6 +9252,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>GUTRON TAB 2.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-71D3BE0A2A0E</t>
         </is>
       </c>
@@ -9055,7 +9280,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9214,6 +9439,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>GUTRON TAB 2.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-78563659C777</t>
         </is>
       </c>
@@ -9237,7 +9467,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9404,6 +9634,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>GYNO-DAKTARIN 1200MG VAGINAL CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-B7A23EB16BBF</t>
         </is>
       </c>
@@ -9427,7 +9662,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9590,6 +9825,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-18205C385A98</t>
         </is>
       </c>
@@ -9613,7 +9853,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9768,6 +10008,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-8782E7949DF6</t>
         </is>
       </c>
@@ -9791,7 +10036,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9958,6 +10203,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>GLUCARE 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-DD56BE26F0BB</t>
         </is>
       </c>
@@ -9981,7 +10231,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10160,6 +10410,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>GLORA 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-B24F9EF34793</t>
         </is>
       </c>
@@ -10183,7 +10438,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10362,6 +10617,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>GLOMOX 500MG CAP</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-42253E11E141</t>
         </is>
       </c>
@@ -10385,7 +10645,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10552,6 +10812,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>GLUCARE 850 TAB.</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-A7F7B2365891</t>
         </is>
       </c>
@@ -10575,7 +10840,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10742,6 +11007,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>GLUCOBAY 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-91F79FA1524E</t>
         </is>
       </c>
@@ -10765,7 +11035,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10928,6 +11198,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>GLUCOBAY 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-28B366A505B6</t>
         </is>
       </c>
@@ -10951,7 +11226,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11128,6 +11403,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>GLUCOPHAGE 1 g tablet</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-E786AC29AEFF</t>
         </is>
       </c>
@@ -11151,7 +11431,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11310,6 +11590,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-1293F68AC743</t>
         </is>
       </c>
@@ -11333,7 +11618,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11492,6 +11777,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-A1039433C916</t>
         </is>
       </c>
@@ -11515,7 +11805,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11674,6 +11964,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>GLYCINE IRRIGATION</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-9A0C17B1B03C</t>
         </is>
       </c>
@@ -11697,7 +11992,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11864,6 +12159,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>GLYCINE 1.5% IRRIGATION SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-DF8DFACD8C6A</t>
         </is>
       </c>
@@ -11887,7 +12187,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12046,6 +12346,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>GLYCINE</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-8B3A083D0444</t>
         </is>
       </c>
@@ -12069,7 +12374,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12232,6 +12537,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>GLYCINE</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-9A8547801225</t>
         </is>
       </c>
@@ -12255,7 +12565,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12418,6 +12728,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-9E46E2584273</t>
         </is>
       </c>
@@ -12441,7 +12756,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12618,6 +12933,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>GLUCOVANCE 2.5/500</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-1BDB0620AC49</t>
         </is>
       </c>
@@ -12641,7 +12961,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12800,6 +13120,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>GLUCOSE 5% I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-B3F66CC11EA7</t>
         </is>
       </c>
@@ -12823,7 +13148,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12986,6 +13311,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>GLUCOSE 10%I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-1ABC9B45E5D0</t>
         </is>
       </c>
@@ -13009,7 +13339,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13182,6 +13512,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>GLUCOPHAGE XR 750MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-B70DDC515151</t>
         </is>
       </c>
@@ -13205,7 +13540,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13384,6 +13719,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>GLUCOPHAGE 850 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-A859BC6A7930</t>
         </is>
       </c>
@@ -13407,7 +13747,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13578,6 +13918,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>GLUCOPHAGE 500 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-53E252D668DF</t>
         </is>
       </c>
@@ -13601,7 +13946,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13778,6 +14123,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>GLUCOVANCE 5/500</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-EEC6C2EBEF5A</t>
         </is>
       </c>
@@ -13801,7 +14151,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13972,6 +14322,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>GLODIP 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-B5FB49CD816F</t>
         </is>
       </c>
@@ -13995,7 +14350,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14170,6 +14525,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>GLOCLAV 375MG TAB</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-1ED70D68DE25</t>
         </is>
       </c>
@@ -14193,7 +14553,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14356,6 +14716,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-FBE1E0DCD644</t>
         </is>
       </c>
@@ -14379,7 +14744,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14538,6 +14903,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>FUSIBACT OINTMENT2%</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-5BD898E09385</t>
         </is>
       </c>
@@ -14561,7 +14931,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14732,6 +15102,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>FUSIBACT CREAM 2% W-W</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-ADAC769CD737</t>
         </is>
       </c>
@@ -14755,7 +15130,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14922,6 +15297,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>FURAZOL TAB</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-16B6D1CD9C57</t>
         </is>
       </c>
@@ -14945,7 +15325,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15104,6 +15484,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>FURAMIDE 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-BD9DB060AA17</t>
         </is>
       </c>
@@ -15127,7 +15512,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15286,6 +15671,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>FUNZOL 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-E80BB6E1AEB4</t>
         </is>
       </c>
@@ -15309,7 +15699,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15472,6 +15862,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>FUNGYZOLE 2% TOPICAL CREAM</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-0311B8E6EC97</t>
         </is>
       </c>
@@ -15495,7 +15890,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15666,6 +16061,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>FUNGO 1% CREAM</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-9A81A169BAFE</t>
         </is>
       </c>
@@ -15689,7 +16089,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15856,6 +16256,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>FUNGIMID 50MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-88DFD06019F7</t>
         </is>
       </c>
@@ -15879,7 +16284,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16046,6 +16451,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>FUNGIMID 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-9668BD7451E5</t>
         </is>
       </c>
@@ -16069,7 +16479,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16232,6 +16642,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>FUDION 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-1874AE663351</t>
         </is>
       </c>
@@ -16255,7 +16670,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16422,6 +16837,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>FUSIDERM 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-B3FEDFFDB148</t>
         </is>
       </c>
@@ -16445,7 +16865,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16612,6 +17032,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>FUSIDERM 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-A5B2019D82D0</t>
         </is>
       </c>
@@ -16635,7 +17060,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16802,6 +17227,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>FUSIDERM B CREAM</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-C42D19149A7D</t>
         </is>
       </c>
@@ -16825,7 +17255,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16980,6 +17410,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>FUSIVER 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-CD72B93CE8F6</t>
         </is>
       </c>
@@ -17003,7 +17438,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17170,6 +17605,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t xml:space="preserve">GALVUS MET </t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-FE5AC4ACCE46</t>
         </is>
       </c>
@@ -17193,7 +17633,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17360,6 +17800,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>GALVUS MET</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-A05D07142DA0</t>
         </is>
       </c>
@@ -17383,7 +17828,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17550,6 +17995,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>GALVUS 50MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-769DF00CAD50</t>
         </is>
       </c>
@@ -17573,7 +18023,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17740,6 +18190,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>GALVUS 50MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-419C5A51BD40</t>
         </is>
       </c>
@@ -17763,7 +18218,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17930,6 +18385,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>FUCIDIN H CREAM</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-A7BD0CF8B78B</t>
         </is>
       </c>
@@ -17953,7 +18413,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18112,6 +18572,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>GABIN 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-996F6AD963B9</t>
         </is>
       </c>
@@ -18135,7 +18600,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18294,6 +18759,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>GABIN 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-1D925A73212F</t>
         </is>
       </c>
@@ -18317,7 +18787,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18476,6 +18946,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>GABIN 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-3E895460DA54</t>
         </is>
       </c>
@@ -18499,7 +18974,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18662,6 +19137,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>GABIN 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-4CEAE6C2ABD9</t>
         </is>
       </c>
@@ -18685,7 +19165,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18840,6 +19320,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>GABIN 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-2F5230CF5403</t>
         </is>
       </c>
@@ -18863,7 +19348,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19026,6 +19511,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>GABANET 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-9F90B3001124</t>
         </is>
       </c>
@@ -19049,7 +19539,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19220,6 +19710,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>GABANET 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-3C119E4274B9</t>
         </is>
       </c>
@@ -19243,7 +19738,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19402,6 +19897,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>FUSIZONE CREAM</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-88AF4FA7CC5F</t>
         </is>
       </c>
@@ -19425,7 +19925,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19579,6 +20079,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>GABIN 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-56FD15C9907A</t>
         </is>
@@ -19595,7 +20100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19641,100 +20146,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19766,7 +20276,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19781,92 +20291,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-34427</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>201.32</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>109</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19898,7 +20413,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19913,92 +20428,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-44893</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>248.1</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>110</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20030,7 +20550,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20045,92 +20565,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-55563</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>231.29</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>111</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20162,7 +20687,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20177,92 +20702,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-26183</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>410.18</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>112</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20294,7 +20824,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20309,92 +20839,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-89426</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>116.05</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>113</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20426,7 +20961,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20441,92 +20976,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-96010</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>282.35</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>114</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20558,7 +21098,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20573,92 +21113,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-74143</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>219.76</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>115</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20690,7 +21235,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20705,92 +21250,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-33734</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>226.05</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>116</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20822,7 +21372,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20837,92 +21387,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-39091</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>327.09</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>117</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20954,7 +21509,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20969,92 +21524,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-57041</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>441.37</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>118</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21086,7 +21646,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21101,92 +21661,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-57259</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>216.3</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>119</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21203,7 +21768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21309,6 +21874,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21344,7 +21919,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21409,6 +21984,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-0230B2993CFE</t>
         </is>
@@ -21445,7 +22030,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21510,6 +22095,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-29F2BAD21264</t>
         </is>
@@ -21546,7 +22141,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21611,6 +22206,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-D850F6DF1FE6</t>
         </is>
@@ -21647,7 +22252,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21712,6 +22317,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-3D65414D2999</t>
         </is>
@@ -21748,7 +22363,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21813,6 +22428,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-3135DA2C2BB7</t>
         </is>
@@ -21849,7 +22474,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21914,6 +22539,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-AC1D29EE3C67</t>
         </is>
@@ -21950,7 +22585,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22015,6 +22650,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-CEE3D8387FC3</t>
         </is>
@@ -22051,7 +22696,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22116,6 +22761,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-D03AEFE8CEDA</t>
         </is>
@@ -22152,7 +22807,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22217,6 +22872,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-F00383C56DF4</t>
         </is>
@@ -22253,7 +22918,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22318,6 +22983,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-80986B270FA5</t>
         </is>
@@ -22354,7 +23029,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22419,6 +23094,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-9EC24DA3FC98</t>
         </is>
@@ -22455,7 +23140,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22520,6 +23205,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F9E562B18060</t>
         </is>
@@ -22556,7 +23251,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22621,6 +23316,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-CF99818AE26E</t>
         </is>
@@ -22657,7 +23362,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22722,6 +23427,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-CC9DED6F9B1B</t>
         </is>
@@ -22758,7 +23473,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22823,6 +23538,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-7664F9F918AB</t>
         </is>
@@ -22859,7 +23584,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22924,6 +23649,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-01DDD580B38C</t>
         </is>
@@ -22960,7 +23695,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23025,6 +23760,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-AE4C96B3FBD4</t>
         </is>
@@ -23061,7 +23806,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23126,6 +23871,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-151F3E159E51</t>
         </is>
@@ -23162,7 +23917,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23227,6 +23982,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-281AB2CC9762</t>
         </is>
@@ -23263,7 +24028,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23328,6 +24093,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-D4BE6186B2FD</t>
         </is>

--- a/product_upload/packages/19/file.xlsx
+++ b/product_upload/packages/19/file.xlsx
@@ -1669,8 +1669,16 @@
           <t>0305781945-452-249635084333</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETATEN 25MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BETATEN 25MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1860,8 +1868,16 @@
           <t>8311625460-437-516514644135</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETATEN 100MG F.C. TABS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>BETATEN 100MG F.C. TABS detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2652,8 +2668,16 @@
           <t>8915656337-946-623184966388</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETAMED-N OINTMENT</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BETAMED-N OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2847,8 +2871,16 @@
           <t>6972223178-553-635013613258</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETAMED-N CREAM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BETAMED-N CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3042,8 +3074,16 @@
           <t>1382375463-688-519255717150</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETAMED 0.1% TOPICAL OINTMENT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BETAMED 0.1% TOPICAL OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3237,8 +3277,16 @@
           <t>7790432507-201-244940778373</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETAMED 0.1% CREAM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BETAMED 0.1% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -4425,8 +4473,16 @@
           <t>4513360879-983-396595051466</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BANEOCIN POWDER</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BANEOCIN POWDER detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4620,8 +4676,16 @@
           <t>0312494543-097-618511883802</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED SALT SOLUTION AMPOULE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>BALANCED SALT SOLUTION AMPOULE detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4807,8 +4871,16 @@
           <t>5353226462-559-959156960149</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CATALIN OPH. SOLUTION</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CATALIN OPH. SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5191,8 +5263,16 @@
           <t>1389524248-080-418691193620</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEKUNIS TABLET</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>BEKUNIS TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5374,8 +5454,16 @@
           <t>0397222647-428-882882821652</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BEFOLVIT 5 MG TAB</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>BEFOLVIT 5 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5772,8 +5860,16 @@
           <t>7760900257-022-390889739004</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BE BE VIT ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>BE BE VIT ORAL DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -6162,8 +6258,16 @@
           <t>1300502810-259-618400019108</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BAUMALGINE OINT</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>BAUMALGINE OINT detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6353,8 +6457,16 @@
           <t>7559518882-343-866798421590</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BATRAMYCIN POWDER</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>BATRAMYCIN POWDER detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6546,8 +6658,16 @@
           <t>5890154114-541-713640515986</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6741,8 +6861,16 @@
           <t>9810644707-111-956553036289</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DEXTROSE 5%+SOD.CHLORIDE 0.20% INJ detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -7533,8 +7661,16 @@
           <t>4899334604-634-998656271319</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GUAPHAN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>GUAPHAN detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7919,8 +8055,16 @@
           <t>9900954564-648-008018003605</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GYNO-DAKTARIN OVULES 400 MG.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>GYNO-DAKTARIN OVULES 400 MG. detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -9101,8 +9245,16 @@
           <t>4197432510-148-843603428255</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GUTRON TAB 2.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>GUTRON TAB 2.5 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9288,8 +9440,16 @@
           <t>1821502935-619-995646902723</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GUTRON TAB 2.5 MG TAB</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>GUTRON TAB 2.5 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9670,8 +9830,16 @@
           <t>3791226765-047-832881333852</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9861,8 +10029,16 @@
           <t>1298384824-628-495615810353</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10848,8 +11024,16 @@
           <t>1961621997-551-520533974187</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLUCOBAY 100MG TAB</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>GLUCOBAY 100MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11043,8 +11227,16 @@
           <t>4412821026-154-623734806876</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLUCOBAY 50MG TAB</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>GLUCOBAY 50MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11439,8 +11631,16 @@
           <t>6654948781-684-795007979483</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11626,8 +11826,16 @@
           <t>5855553193-242-159900796031</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11813,8 +12021,16 @@
           <t>0728822904-197-108243014638</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE IRRIGATION</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>GLYCINE IRRIGATION detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -12000,8 +12216,16 @@
           <t>6404558073-642-114422739467</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE 1.5% IRRIGATION SOLUTION</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>GLYCINE 1.5% IRRIGATION SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12195,8 +12419,16 @@
           <t>4132815330-081-353966629702</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>GLYCINE detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12382,8 +12614,16 @@
           <t>1464158224-131-861854954018</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>GLYCINE detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12573,8 +12813,16 @@
           <t>7315879666-178-791986093011</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLYCINE IRRIGATION SOLN 1.5%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>GLYCINE IRRIGATION SOLN 1.5% detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12969,8 +13217,16 @@
           <t>2918688028-555-247928145737</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLUCOSE 5% I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>GLUCOSE 5% I.V INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13156,8 +13412,16 @@
           <t>5422083572-808-855856317633</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLUCOSE 10%I.V INFUSION</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>GLUCOSE 10%I.V INFUSION detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -14159,8 +14423,16 @@
           <t>5510681640-152-580476167850</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLODIP 5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GLODIP 5MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14561,8 +14833,16 @@
           <t>4018059103-862-669154365647</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>FUSIBACT-B CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14752,8 +15032,16 @@
           <t>0907042303-519-136824431318</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIBACT OINTMENT2%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>FUSIBACT OINTMENT2% detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -15333,8 +15621,16 @@
           <t>7460155740-811-388443272533</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FURAMIDE 500MG TAB</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>FURAMIDE 500MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15520,8 +15816,16 @@
           <t>6487015783-519-671212978520</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUNZOL 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>FUNZOL 150MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15707,8 +16011,16 @@
           <t>2235837476-384-335187510842</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUNGYZOLE 2% TOPICAL CREAM</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>FUNGYZOLE 2% TOPICAL CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -16097,8 +16409,16 @@
           <t>6901484852-784-406023768756</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUNGIMID 50MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>FUNGIMID 50MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16292,8 +16612,16 @@
           <t>1806744871-724-397127002900</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUNGIMID 150MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>FUNGIMID 150MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16487,8 +16815,16 @@
           <t>8546520337-541-358807384184</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUDION 2% CREAM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>FUDION 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -17263,8 +17599,16 @@
           <t>7597454066-371-957493299243</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIVER 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>FUSIVER 2% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -18421,8 +18765,16 @@
           <t>5671770189-686-542581881692</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABIN 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>GABIN 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18608,8 +18960,16 @@
           <t>4972261680-950-894370622806</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABIN 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>GABIN 300MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18795,8 +19155,16 @@
           <t>4867100127-565-105263635191</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABIN 300MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>GABIN 300MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18982,8 +19350,16 @@
           <t>7196024932-383-662061236286</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABIN 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>GABIN 100MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19173,8 +19549,16 @@
           <t>6445321977-347-269081905463</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABIN 100MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>GABIN 100MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19356,8 +19740,16 @@
           <t>0046251364-170-109254045980</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABANET 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>GABANET 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19746,8 +20138,16 @@
           <t>4348034668-214-183841800073</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIZONE CREAM</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>FUSIZONE CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19933,8 +20333,16 @@
           <t>2175440577-388-947226849333</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GABIN 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>GABIN 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/19/file.xlsx
+++ b/product_upload/packages/19/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22176,7 +22176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22257,40 +22257,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22370,38 +22375,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>342.3</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-0230B2993CFE</t>
         </is>
@@ -22481,38 +22491,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>328.91</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-29F2BAD21264</t>
         </is>
@@ -22592,38 +22607,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>484.04</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-D850F6DF1FE6</t>
         </is>
@@ -22703,38 +22723,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>328.72</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-3D65414D2999</t>
         </is>
@@ -22814,38 +22839,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>206.88</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-3135DA2C2BB7</t>
         </is>
@@ -22925,38 +22955,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>189.21</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-AC1D29EE3C67</t>
         </is>
@@ -23036,38 +23071,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>133.31</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-CEE3D8387FC3</t>
         </is>
@@ -23147,38 +23187,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>426.54</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-D03AEFE8CEDA</t>
         </is>
@@ -23258,38 +23303,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>195.45</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-F00383C56DF4</t>
         </is>
@@ -23369,38 +23419,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>203.5</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-80986B270FA5</t>
         </is>
@@ -23480,38 +23535,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>84.69</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-9EC24DA3FC98</t>
         </is>
@@ -23591,38 +23651,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>80.06</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F9E562B18060</t>
         </is>
@@ -23702,38 +23767,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>258.57</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-CF99818AE26E</t>
         </is>
@@ -23813,38 +23883,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>365.35</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-CC9DED6F9B1B</t>
         </is>
@@ -23924,38 +23999,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>189.17</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-7664F9F918AB</t>
         </is>
@@ -24035,38 +24115,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>134.93</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-01DDD580B38C</t>
         </is>
@@ -24146,38 +24231,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>434</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-AE4C96B3FBD4</t>
         </is>
@@ -24257,38 +24347,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>56.96</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-151F3E159E51</t>
         </is>
@@ -24368,38 +24463,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>403.35</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-281AB2CC9762</t>
         </is>
@@ -24479,38 +24579,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>326.57</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-D4BE6186B2FD</t>
         </is>
